--- a/tables/enemdu_ingreso_hogar_2026_03_summary.xlsx
+++ b/tables/enemdu_ingreso_hogar_2026_03_summary.xlsx
@@ -428,13 +428,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1100.44578313253</v>
+        <v>883.616250117475</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>699.512389380531</v>
+        <v>577.911859852234</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1239.03701437749</v>
+        <v>1016.25195176864</v>
       </c>
     </row>
     <row r="3">
@@ -442,13 +442,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>495</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4">
@@ -456,13 +456,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>736</v>
+        <v>630</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>460</v>
+        <v>376</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>848</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5">
@@ -470,13 +470,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1320</v>
+        <v>1071</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>852.25</v>
+        <v>692</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1474.75</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -484,13 +484,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>421</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>590</v>
+        <v>513</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>691.8</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -512,13 +512,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>915.2</v>
+        <v>754</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>580</v>
+        <v>492</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1032</v>
+        <v>885</v>
       </c>
     </row>
     <row r="9">
@@ -526,13 +526,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1500</v>
+        <v>1223</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1002.2</v>
+        <v>810</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1659</v>
+        <v>1362</v>
       </c>
     </row>
   </sheetData>

--- a/tables/enemdu_ingreso_hogar_2026_03_summary.xlsx
+++ b/tables/enemdu_ingreso_hogar_2026_03_summary.xlsx
@@ -428,13 +428,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>883.616250117475</v>
+        <v>884.938277133758</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>577.911859852234</v>
+        <v>581.601580952393</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1016.25195176864</v>
+        <v>1016.54670938314</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +459,7 @@
         <v>630</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>722</v>
@@ -470,10 +470,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>1200</v>
@@ -484,7 +484,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>155</v>
@@ -498,7 +498,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>280</v>
@@ -512,10 +512,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>885</v>
@@ -526,10 +526,10 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1362</v>
